--- a/back/storage/app/ads/2026-09/sept-meta.xlsx
+++ b/back/storage/app/ads/2026-09/sept-meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE616DE-8278-4B15-84AF-8F91F0F61001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5CA10C-CA0E-4F66-A9C3-1B2F7BCCC821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1708,7 +1708,7 @@
         <v>4</v>
       </c>
       <c r="M16" s="15">
-        <v>68115</v>
+        <v>638115</v>
       </c>
       <c r="N16" s="15">
         <v>17028.75</v>
